--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-169</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 1.603.488,10</t>
-  </si>
-  <si>
-    <t>R$ 8.908,27
-R$ 9.096,00</t>
-  </si>
-  <si>
-    <t>(5.3%)
-(3.3%)</t>
+172</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.627.693,84</t>
+  </si>
+  <si>
+    <t>R$ 8.894,50
+R$ 9.078,08</t>
+  </si>
+  <si>
+    <t>(5.4%)
+(3.4%)</t>
   </si>
   <si>
     <t>97.2</t>
   </si>
   <si>
-    <t>(9.6%)</t>
-  </si>
-  <si>
-    <t>(43.9%)</t>
-  </si>
-  <si>
-    <t>(86.7%)</t>
+    <t>(9.5%)</t>
+  </si>
+  <si>
+    <t>(42.4%)</t>
+  </si>
+  <si>
+    <t>(85.0%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -950,10 +950,10 @@
     <t>29.3</t>
   </si>
   <si>
-    <t>60.3%</t>
-  </si>
-  <si>
-    <t>14.9%</t>
+    <t>59.8%</t>
+  </si>
+  <si>
+    <t>14.8%</t>
   </si>
   <si>
     <t>6.5</t>
@@ -965,16 +965,16 @@
     <t>14.5</t>
   </si>
   <si>
-    <t>21.1</t>
+    <t>21.0</t>
   </si>
   <si>
     <t>64.0%</t>
   </si>
   <si>
-    <t>-R$ 49.962,51</t>
-  </si>
-  <si>
-    <t>2.94</t>
+    <t>-R$ 50.220,51</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2213,10 +2213,10 @@
         <v>0.21649484536082464</v>
       </c>
       <c r="T7" s="6">
-        <v>0.33255816226875851</v>
+        <v>0.32417071710357492</v>
       </c>
       <c r="U7" s="6">
-        <v>0.023635232268391929</v>
+        <v>0.015247787103208359</v>
       </c>
       <c r="V7" s="6">
         <v>0.030735084976928721</v>
@@ -10886,7 +10886,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10920,25 +10920,59 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
+      <c r="O76" s="5">
+        <v>8665.1100000000006</v>
+      </c>
+      <c r="P76" s="5">
+        <v>8665.1100000000006</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.19713083312022595</v>
+      </c>
+      <c r="R76" s="7">
+        <v>111</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.15267175572519087</v>
+      </c>
+      <c r="T76" s="6">
+        <v>1.1431260653355813</v>
+      </c>
+      <c r="U76" s="6">
+        <v>0.78649239305675278</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.016093679133905973</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.0029320458713161172</v>
+      </c>
+      <c r="X76" s="8">
+        <v>25.89229125</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.33750000000000002</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.1125</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>2.9853798245614036</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>5.4186863636363638</v>
+      </c>
       <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="AD76" s="8">
+        <v>15.71979125</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.69999999999999996</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-71.799999999999997</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -16809,7 +16843,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -22924,7 +22958,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>44</v>
@@ -22960,25 +22994,61 @@
       <c t="s" r="N172" s="4">
         <v>52</v>
       </c>
-      <c r="O172" s="5"/>
-      <c r="P172" s="5"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="7"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="8"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-      <c r="AA172" s="8"/>
-      <c r="AB172" s="8"/>
-      <c r="AC172" s="8"/>
-      <c r="AD172" s="8"/>
-      <c r="AE172" s="6"/>
+      <c r="O172" s="5">
+        <v>3205.3000000000002</v>
+      </c>
+      <c r="P172" s="5">
+        <v>3205.3000000000002</v>
+      </c>
+      <c r="Q172" s="6">
+        <v>-0.15173632981003837</v>
+      </c>
+      <c r="R172" s="7">
+        <v>41</v>
+      </c>
+      <c r="S172" s="6">
+        <v>0.051282051282051322</v>
+      </c>
+      <c r="T172" s="6">
+        <v>0.28896724175584187</v>
+      </c>
+      <c r="U172" s="6">
+        <v>0.0090121673478301568</v>
+      </c>
+      <c r="V172" s="6">
+        <v>0.04312997223348828</v>
+      </c>
+      <c r="W172" s="6">
+        <v>-0.008755966680185941</v>
+      </c>
+      <c r="X172" s="8">
+        <v>20.898275862068964</v>
+      </c>
+      <c r="Y172" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="8">
+        <v>4.3780487804878048</v>
+      </c>
+      <c r="AB172" s="8">
+        <v>3.9362068965517243</v>
+      </c>
+      <c r="AC172" s="8">
+        <v>8.1965500000000002</v>
+      </c>
+      <c r="AD172" s="8">
+        <v>15.160344827586206</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>0.93103448275862066</v>
+      </c>
       <c r="AF172" s="9"/>
-      <c r="AG172" s="5"/>
+      <c r="AG172" s="5">
+        <v>0</v>
+      </c>
       <c r="AH172" s="10">
         <v>1</v>
       </c>
@@ -25851,7 +25921,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25887,25 +25957,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>12335.33</v>
+      </c>
+      <c r="P195" s="5">
+        <v>12335.33</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.061372080336876689</v>
+      </c>
+      <c r="R195" s="7">
+        <v>134</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.021897810218978075</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.31305048182740147</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.0069490641920402609</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.018173206553857905</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0048375276543067757</v>
+      </c>
+      <c r="X195" s="8">
+        <v>29.744167000000001</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>4.6276083969465649</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>10.760999999999999</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>22.3825</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.53000000000000003</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-186.19999999999999</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.627.693,84</t>
-  </si>
-  <si>
-    <t>R$ 8.894,50
-R$ 9.078,08</t>
-  </si>
-  <si>
-    <t>(5.4%)
-(3.4%)</t>
-  </si>
-  <si>
-    <t>97.2</t>
-  </si>
-  <si>
-    <t>(9.5%)</t>
-  </si>
-  <si>
-    <t>(42.4%)</t>
-  </si>
-  <si>
-    <t>(85.0%)</t>
+174</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.647.236,83</t>
+  </si>
+  <si>
+    <t>R$ 8.903,98
+R$ 9.086,05</t>
+  </si>
+  <si>
+    <t>(5.7%)
+(3.7%)</t>
+  </si>
+  <si>
+    <t>97.4</t>
+  </si>
+  <si>
+    <t>(9.8%)</t>
+  </si>
+  <si>
+    <t>(41.5%)</t>
+  </si>
+  <si>
+    <t>(84.1%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -947,31 +947,31 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>29.3</t>
-  </si>
-  <si>
-    <t>59.8%</t>
-  </si>
-  <si>
-    <t>14.8%</t>
-  </si>
-  <si>
-    <t>6.5</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>59.5%</t>
+  </si>
+  <si>
+    <t>15.1%</t>
+  </si>
+  <si>
+    <t>6.6</t>
   </si>
   <si>
     <t>7.9</t>
   </si>
   <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>21.0</t>
-  </si>
-  <si>
-    <t>64.0%</t>
-  </si>
-  <si>
-    <t>-R$ 50.220,51</t>
+    <t>14.6</t>
+  </si>
+  <si>
+    <t>21.3</t>
+  </si>
+  <si>
+    <t>63.8%</t>
+  </si>
+  <si>
+    <t>-R$ 50.752,61</t>
   </si>
   <si>
     <t>2.95</t>
@@ -2947,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2983,25 +2983,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>9804.9599999999991</v>
+      </c>
+      <c r="P13" s="5">
+        <v>9804.9599999999991</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.30323405888246968</v>
+      </c>
+      <c r="R13" s="7">
+        <v>113</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.29813664596273293</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.40240450751456414</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.0027424997144302478</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.038532385649711981</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.036487502243762349</v>
+      </c>
+      <c r="X13" s="8">
+        <v>63.67307692307692</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.64835164835164838</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>26.487262601626018</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>16.371852222222223</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>46.794195000000002</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>53.51391978021978</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.27472527472527475</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-84.900000000000006</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -5646,10 +5682,10 @@
         <v>0.035714285714285809</v>
       </c>
       <c r="T34" s="6">
-        <v>0.28788521798086597</v>
+        <v>0.30534807131743069</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.050605691150593136</v>
+        <v>-0.033142837814028415</v>
       </c>
       <c r="V34" s="6">
         <v>0.057151555115783403</v>
@@ -8658,7 +8694,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8694,25 +8730,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>9738.0300000000007</v>
+      </c>
+      <c r="P58" s="5">
+        <v>9738.0300000000007</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.16650147389611847</v>
+      </c>
+      <c r="R58" s="7">
+        <v>115</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.21232876712328763</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.23016885345393265</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.12147413799300268</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.012061885206761531</v>
+      </c>
+      <c r="W58" s="6">
+        <v>0.00029667191413458366</v>
+      </c>
+      <c r="X58" s="8">
+        <v>26.026907228915661</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.3493975903614458</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>4.1070567567567569</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>5.2524096385542167</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>9.6428560000000001</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>16.523695180722893</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.79518072289156627</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-447.19999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -10962,7 +11034,9 @@
       <c r="AB76" s="8">
         <v>5.4186863636363638</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>8.3176690000000004</v>
+      </c>
       <c r="AD76" s="8">
         <v>15.71979125</v>
       </c>
@@ -23949,7 +24023,9 @@
       <c r="AB179" s="8">
         <v>1.6966273809523809</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>10.384861000000001</v>
+      </c>
       <c r="AD179" s="8">
         <v>17.263529411764708</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-20).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.647.236,83</t>
-  </si>
-  <si>
-    <t>R$ 8.903,98
-R$ 9.086,05</t>
-  </si>
-  <si>
-    <t>(5.7%)
+180</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.693.171,36</t>
+  </si>
+  <si>
+    <t>R$ 8.864,77
+R$ 9.038,37</t>
+  </si>
+  <si>
+    <t>(5.6%)
 (3.7%)</t>
   </si>
   <si>
-    <t>97.4</t>
-  </si>
-  <si>
-    <t>(9.8%)</t>
-  </si>
-  <si>
-    <t>(41.5%)</t>
-  </si>
-  <si>
-    <t>(84.1%)</t>
+    <t>96.9</t>
+  </si>
+  <si>
+    <t>(9.7%)</t>
+  </si>
+  <si>
+    <t>(39.0%)</t>
+  </si>
+  <si>
+    <t>(81.3%)</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -947,34 +947,34 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>59.5%</t>
-  </si>
-  <si>
-    <t>15.1%</t>
+    <t>29.4</t>
+  </si>
+  <si>
+    <t>60.3%</t>
+  </si>
+  <si>
+    <t>14.8%</t>
   </si>
   <si>
     <t>6.6</t>
   </si>
   <si>
-    <t>7.9</t>
-  </si>
-  <si>
-    <t>14.6</t>
-  </si>
-  <si>
-    <t>21.3</t>
-  </si>
-  <si>
-    <t>63.8%</t>
-  </si>
-  <si>
-    <t>-R$ 50.752,61</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>21.1</t>
+  </si>
+  <si>
+    <t>64.3%</t>
+  </si>
+  <si>
+    <t>-R$ 51.290,41</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>15754.02</v>
+      </c>
+      <c r="P6" s="5">
+        <v>15754.02</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.39310452161502307</v>
+      </c>
+      <c r="R6" s="7">
+        <v>177</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.32089552238805963</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.29302328548522855</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.015316427172239211</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.026350207756496435</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0032824447347407199</v>
+      </c>
+      <c r="X6" s="8">
+        <v>22.717832167832167</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.8601398601398601</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.027972027972027972</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>6.6598870056497175</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.142605633802817</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>9.9799009999999999</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>16.903962937062939</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.92307692307692313</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4360,7 +4396,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4396,25 +4432,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>8911.2299999999996</v>
+      </c>
+      <c r="P24" s="5">
+        <v>8911.2299999999996</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.00058275058275047975</v>
+      </c>
+      <c r="R24" s="7">
+        <v>110</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.098360655737704916</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0.0054672587285930227</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.34528117891693966</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.026083380184329211</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.0078468404473905403</v>
+      </c>
+      <c r="X24" s="8">
+        <v>25.146052631578947</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.3408953703703705</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>7.0855263157894735</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>17.283990789473684</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-317.80000000000001</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5896,7 +5966,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5932,25 +6002,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>7489.0699999999997</v>
+      </c>
+      <c r="P36" s="5">
+        <v>7489.0699999999997</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.3722729788068353</v>
+      </c>
+      <c r="R36" s="7">
+        <v>75</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.36363636363636354</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.29175578543130187</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.0071451461930520082</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.066915718507104358</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.037729183997478995</v>
+      </c>
+      <c r="X36" s="8">
+        <v>24.185676562499999</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.9375</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.046875</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>4.0861842105263158</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>5.0375711864406778</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>8.2912149999999993</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>14.410676562500001</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.828125</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7817,7 +7923,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7853,25 +7959,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1308.1800000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1308.1800000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.13144685823551283</v>
+      </c>
+      <c r="R51" s="7">
+        <v>13</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.23529411764705888</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.32278432631595039</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.0190524239783516</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.078801082419850468</v>
+      </c>
+      <c r="X51" s="8">
+        <v>18.252783333333333</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>2.1166692307692307</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>6.6666600000000003</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>8.6416660000000007</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>14.255549999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12576,7 +12718,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12615,7 +12757,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12649,25 +12791,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>8173.3999999999996</v>
+      </c>
+      <c r="P89" s="5">
+        <v>8173.3999999999996</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.3664875690993139</v>
+      </c>
+      <c r="R89" s="7">
+        <v>83</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.37121212121212122</v>
+      </c>
+      <c r="T89" s="6">
+        <v>1.7181138938507843</v>
+      </c>
+      <c r="U89" s="6">
+        <v>1.3921809895514718</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.022079917782073556</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0085885922627058509</v>
+      </c>
+      <c r="X89" s="8">
+        <v>33.057525806451615</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>8.9841662499999995</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>4.1938899999999997</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>20.327958064516128</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.32258064516129031</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-220</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16655,7 +16831,7 @@
         <v>-435.39999999999998</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18618,7 +18794,7 @@
         <v>-453.10000000000002</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20896,7 +21072,7 @@
         <v>100</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21290,7 +21466,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21326,25 +21502,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>4298.6300000000001</v>
+      </c>
+      <c r="P158" s="5">
+        <v>4298.6300000000001</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.45170255970693729</v>
+      </c>
+      <c r="R158" s="7">
+        <v>43</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.41891891891891897</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.3085018715265096</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.0090901985051051147</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.020704503527868182</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0090375305620627958</v>
+      </c>
+      <c r="X158" s="8">
+        <v>29.630645161290321</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>3.9575749999999998</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>6.1365580645161293</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>10.176142</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>17.067203225806452</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.61290322580645162</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -26075,7 +26287,9 @@
       <c r="AB195" s="8">
         <v>10.760999999999999</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>15.4655</v>
+      </c>
       <c r="AD195" s="8">
         <v>22.3825</v>
       </c>
